--- a/fixtures/sml/filtering/sort-state.xlsx
+++ b/fixtures/sml/filtering/sort-state.xlsx
@@ -10,10 +10,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t>Beta</t>
+    <t>Alpha</t>
   </si>
   <si>
-    <t>Alpha</t>
+    <t>Beta</t>
   </si>
   <si>
     <t>Gamma</t>
@@ -26,12 +26,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
